--- a/output/yearly_benthic_cover_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_6_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.03099345318039</v>
+        <v>45.4484642750741</v>
       </c>
       <c r="M2" t="n">
-        <v>100.8329886782314</v>
+        <v>99.79120636112299</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9719330205851</v>
+        <v>87.98504916991385</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89263336587263</v>
+        <v>45.93464719069895</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228615838776984</v>
+        <v>2.228617637406825</v>
       </c>
       <c r="E3" t="n">
-        <v>5.68276836523161</v>
+        <v>5.707339354876392</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428719462589948</v>
+        <v>0.7428725458022749</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96118118405277</v>
+        <v>33.97565583576932</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17210952791375</v>
+        <v>34.17213710690464</v>
       </c>
       <c r="I3" t="n">
-        <v>6.541436494232278</v>
+        <v>6.515473277890184</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642949664118717</v>
+        <v>4.642953411264218</v>
       </c>
       <c r="K3" t="n">
-        <v>12.02806697941489</v>
+        <v>12.01495083008616</v>
       </c>
       <c r="L3" t="n">
-        <v>48.84448353681852</v>
+        <v>48.8165180444015</v>
       </c>
       <c r="M3" t="n">
-        <v>106.765183882106</v>
+        <v>106.7661160651866</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.08664074140457</v>
+        <v>87.03374953111587</v>
       </c>
       <c r="C4" t="n">
-        <v>42.63867790156098</v>
+        <v>42.60811257920824</v>
       </c>
       <c r="D4" t="n">
-        <v>2.186058463434118</v>
+        <v>2.182571638735644</v>
       </c>
       <c r="E4" t="n">
-        <v>6.484683382756448</v>
+        <v>6.496231207189331</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444251919297742</v>
+        <v>0.7444205571176626</v>
       </c>
       <c r="G4" t="n">
-        <v>33.31266262397201</v>
+        <v>33.27367673571755</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24355882876961</v>
+        <v>34.24334562741247</v>
       </c>
       <c r="I4" t="n">
-        <v>5.462594800981524</v>
+        <v>5.440875282957815</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652657449561088</v>
+        <v>4.652628481985391</v>
       </c>
       <c r="K4" t="n">
-        <v>12.91335925859542</v>
+        <v>12.96625046888413</v>
       </c>
       <c r="L4" t="n">
-        <v>44.26625627055937</v>
+        <v>44.24465158307734</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81829343071577</v>
+        <v>99.81901463116971</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.97551596136466</v>
+        <v>85.65858973049203</v>
       </c>
       <c r="C5" t="n">
-        <v>42.375398604411</v>
+        <v>42.07741746076939</v>
       </c>
       <c r="D5" t="n">
-        <v>2.131965376325168</v>
+        <v>2.114760419124912</v>
       </c>
       <c r="E5" t="n">
-        <v>7.084257763153752</v>
+        <v>7.051409907750909</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457413556741299</v>
+        <v>0.7457363291499316</v>
       </c>
       <c r="G5" t="n">
-        <v>32.48835495274951</v>
+        <v>32.23988313172417</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30410236100997</v>
+        <v>34.30387114089685</v>
       </c>
       <c r="I5" t="n">
-        <v>4.560210679488832</v>
+        <v>4.54207674465819</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660883472963311</v>
+        <v>4.660852057187072</v>
       </c>
       <c r="K5" t="n">
-        <v>14.02448403863531</v>
+        <v>14.34141026950796</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44837861248197</v>
+        <v>43.43003684519604</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84826125552829</v>
+        <v>99.8488645754734</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.6510666417517</v>
+        <v>84.0324732043197</v>
       </c>
       <c r="C6" t="n">
-        <v>41.75923272266304</v>
+        <v>41.15651725389122</v>
       </c>
       <c r="D6" t="n">
-        <v>2.067352260819759</v>
+        <v>2.034763682238788</v>
       </c>
       <c r="E6" t="n">
-        <v>7.503868140045612</v>
+        <v>7.416463159096177</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468589612711004</v>
+        <v>0.7468576829896115</v>
       </c>
       <c r="G6" t="n">
-        <v>31.50373585224563</v>
+        <v>31.02031923937784</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35551221847061</v>
+        <v>34.35545341752212</v>
       </c>
       <c r="I6" t="n">
-        <v>3.805870700954607</v>
+        <v>3.79075550441009</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667868507944377</v>
+        <v>4.667860518685072</v>
       </c>
       <c r="K6" t="n">
-        <v>15.34893335824828</v>
+        <v>15.9675267956803</v>
       </c>
       <c r="L6" t="n">
-        <v>42.76516140021398</v>
+        <v>42.74978715196574</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87332748112532</v>
+        <v>99.87383120153726</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.19776203069739</v>
+        <v>82.17583162147088</v>
       </c>
       <c r="C7" t="n">
-        <v>40.89710375623814</v>
+        <v>39.88825600091057</v>
       </c>
       <c r="D7" t="n">
-        <v>1.996742923683673</v>
+        <v>1.943909318942483</v>
       </c>
       <c r="E7" t="n">
-        <v>7.776843127321207</v>
+        <v>7.612479514498316</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478091955341254</v>
+        <v>0.7478159220575581</v>
       </c>
       <c r="G7" t="n">
-        <v>30.42774220181889</v>
+        <v>29.63522898130872</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39922299456975</v>
+        <v>34.39953241464766</v>
       </c>
       <c r="I7" t="n">
-        <v>3.175594115681454</v>
+        <v>3.163015957156398</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673807472088283</v>
+        <v>4.673849512859737</v>
       </c>
       <c r="K7" t="n">
-        <v>16.80223796930261</v>
+        <v>17.82416837852911</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19493964387716</v>
+        <v>42.18227685654894</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89428136941791</v>
+        <v>99.89470123598862</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.19191836352971</v>
+        <v>87.19521770944549</v>
       </c>
       <c r="C8" t="n">
-        <v>43.24610071392412</v>
+        <v>42.24005463977129</v>
       </c>
       <c r="D8" t="n">
-        <v>2.001041353536048</v>
+        <v>1.948148447106641</v>
       </c>
       <c r="E8" t="n">
-        <v>9.644610771705672</v>
+        <v>9.483086563477228</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494190198794821</v>
+        <v>0.7494467015933675</v>
       </c>
       <c r="G8" t="n">
-        <v>30.94412634561014</v>
+        <v>30.15148679501277</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47327491445616</v>
+        <v>34.47454827329489</v>
       </c>
       <c r="I8" t="n">
-        <v>5.695577084095434</v>
+        <v>5.704459044002043</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683868874246763</v>
+        <v>4.684041884958546</v>
       </c>
       <c r="K8" t="n">
-        <v>11.80808163647029</v>
+        <v>12.80478229055452</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75637290176857</v>
+        <v>44.76542819412041</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81055525216298</v>
+        <v>99.81026512444622</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.3342725072462</v>
+        <v>85.01893920736295</v>
       </c>
       <c r="C9" t="n">
-        <v>42.27260400723885</v>
+        <v>40.94817598344109</v>
       </c>
       <c r="D9" t="n">
-        <v>1.917275052352017</v>
+        <v>1.849637237474758</v>
       </c>
       <c r="E9" t="n">
-        <v>10.03337896694722</v>
+        <v>9.79732467013973</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507948768864212</v>
+        <v>0.7508461188464982</v>
       </c>
       <c r="G9" t="n">
-        <v>29.64876330737876</v>
+        <v>28.62682914339087</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53656433677536</v>
+        <v>34.53892146693891</v>
       </c>
       <c r="I9" t="n">
-        <v>4.755027986366284</v>
+        <v>4.76259232778158</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692467980540132</v>
+        <v>4.692788242790614</v>
       </c>
       <c r="K9" t="n">
-        <v>13.6657274927538</v>
+        <v>14.98106079263704</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90345802544912</v>
+        <v>43.91230602825514</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84178952544178</v>
+        <v>99.84154280433327</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.32823349363861</v>
+        <v>82.61144664281649</v>
       </c>
       <c r="C10" t="n">
-        <v>41.00459374361881</v>
+        <v>39.27861576194174</v>
       </c>
       <c r="D10" t="n">
-        <v>1.827681458796421</v>
+        <v>1.741858770633973</v>
       </c>
       <c r="E10" t="n">
-        <v>10.22597927154726</v>
+        <v>9.888966143059895</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519726988460097</v>
+        <v>0.7520504548178754</v>
       </c>
       <c r="G10" t="n">
-        <v>28.26328695335815</v>
+        <v>26.95874218391761</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59074414691644</v>
+        <v>34.59432092162226</v>
       </c>
       <c r="I10" t="n">
-        <v>3.968739596386767</v>
+        <v>3.975192826153171</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699829367787561</v>
+        <v>4.700315342611721</v>
       </c>
       <c r="K10" t="n">
-        <v>15.6717665063614</v>
+        <v>17.3885533571835</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19155563928739</v>
+        <v>43.2005366495475</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86791588926761</v>
+        <v>99.86770576867274</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.19035782662162</v>
+        <v>80.05574644144352</v>
       </c>
       <c r="C11" t="n">
-        <v>39.48225854836234</v>
+        <v>37.33802746579985</v>
       </c>
       <c r="D11" t="n">
-        <v>1.733090109550774</v>
+        <v>1.628745935778692</v>
       </c>
       <c r="E11" t="n">
-        <v>10.24868959351077</v>
+        <v>9.799669102720124</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529826822097326</v>
+        <v>0.7530892014010498</v>
       </c>
       <c r="G11" t="n">
-        <v>26.80052524826563</v>
+        <v>25.20809522908688</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63720338164769</v>
+        <v>34.64210326444828</v>
       </c>
       <c r="I11" t="n">
-        <v>3.311725047626195</v>
+        <v>3.317236199251921</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706141763810828</v>
+        <v>4.706807508756562</v>
       </c>
       <c r="K11" t="n">
-        <v>17.8096421733784</v>
+        <v>19.94425355855649</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59785651169297</v>
+        <v>42.60729695269495</v>
       </c>
       <c r="M11" t="n">
-        <v>99.8897572334337</v>
+        <v>99.88957797705129</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>79.88043797567599</v>
+        <v>77.40362058515039</v>
       </c>
       <c r="C12" t="n">
-        <v>37.6853295947616</v>
+        <v>35.19820086258973</v>
       </c>
       <c r="D12" t="n">
-        <v>1.631744376060283</v>
+        <v>1.512641352751869</v>
       </c>
       <c r="E12" t="n">
-        <v>10.10987014465596</v>
+        <v>9.562379504504234</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538508361795964</v>
+        <v>0.7539867879910905</v>
       </c>
       <c r="G12" t="n">
-        <v>25.23331366806686</v>
+        <v>23.41114499812632</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67713846426142</v>
+        <v>34.68339224759015</v>
       </c>
       <c r="I12" t="n">
-        <v>2.762952760329379</v>
+        <v>2.767658269242405</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711567726122476</v>
+        <v>4.712417424944316</v>
       </c>
       <c r="K12" t="n">
-        <v>20.11956202432402</v>
+        <v>22.59637941484961</v>
       </c>
       <c r="L12" t="n">
-        <v>42.10311601848034</v>
+        <v>42.11327427258144</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90800763756596</v>
+        <v>99.90785455002079</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.55777311785768</v>
+        <v>74.78376265279829</v>
       </c>
       <c r="C13" t="n">
-        <v>35.78985760607904</v>
+        <v>33.00469169286063</v>
       </c>
       <c r="D13" t="n">
-        <v>1.530757401736109</v>
+        <v>1.399166824399931</v>
       </c>
       <c r="E13" t="n">
-        <v>9.868304277214227</v>
+        <v>9.229826537527092</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754597561753883</v>
+        <v>0.754762701087761</v>
       </c>
       <c r="G13" t="n">
-        <v>23.67164994371355</v>
+        <v>21.65490011429563</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71148784067861</v>
+        <v>34.71908425003699</v>
       </c>
       <c r="I13" t="n">
-        <v>2.304741331799538</v>
+        <v>2.308755343652386</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716234760961768</v>
+        <v>4.717266881798506</v>
       </c>
       <c r="K13" t="n">
-        <v>22.44222688214232</v>
+        <v>25.21623734720172</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69116682399171</v>
+        <v>41.7021915635698</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92325131221307</v>
+        <v>99.92312060363214</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.03099001749177</v>
+        <v>82.07826438131377</v>
       </c>
       <c r="C14" t="n">
-        <v>39.8572756031286</v>
+        <v>37.64640906283169</v>
       </c>
       <c r="D14" t="n">
-        <v>1.532504355428022</v>
+        <v>1.400778625612142</v>
       </c>
       <c r="E14" t="n">
-        <v>12.13759798506936</v>
+        <v>11.78336917120792</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554587347881727</v>
+        <v>0.7556321666978155</v>
       </c>
       <c r="G14" t="n">
-        <v>25.47720103973939</v>
+        <v>23.74999671402901</v>
       </c>
       <c r="H14" t="n">
-        <v>36.52963798443752</v>
+        <v>36.82923042603199</v>
       </c>
       <c r="I14" t="n">
-        <v>2.876972825603248</v>
+        <v>2.836556235873558</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721617092426079</v>
+        <v>4.722701041861346</v>
       </c>
       <c r="K14" t="n">
-        <v>15.96900998250819</v>
+        <v>17.92173561868623</v>
       </c>
       <c r="L14" t="n">
-        <v>44.07792463880646</v>
+        <v>44.33741223974925</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90421022444326</v>
+        <v>99.90555692126716</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.38411645516359</v>
+        <v>81.12109963958127</v>
       </c>
       <c r="C15" t="n">
-        <v>39.65428346957849</v>
+        <v>37.12657807968575</v>
       </c>
       <c r="D15" t="n">
-        <v>1.508487734641067</v>
+        <v>1.365803436047258</v>
       </c>
       <c r="E15" t="n">
-        <v>12.34853245129041</v>
+        <v>11.88350656959434</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561834662331774</v>
+        <v>0.7563668286394191</v>
       </c>
       <c r="G15" t="n">
-        <v>25.07912121509202</v>
+        <v>23.15699749056104</v>
       </c>
       <c r="H15" t="n">
-        <v>36.5658676061616</v>
+        <v>36.86503757549573</v>
       </c>
       <c r="I15" t="n">
-        <v>2.399777317787946</v>
+        <v>2.366095060247138</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726146663957359</v>
+        <v>4.727292678996369</v>
       </c>
       <c r="K15" t="n">
-        <v>16.61588354483641</v>
+        <v>18.8789003604187</v>
       </c>
       <c r="L15" t="n">
-        <v>43.64991707376277</v>
+        <v>43.91572833112131</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92008408817767</v>
+        <v>99.92120677122576</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.02174677191152</v>
+        <v>78.41359655090127</v>
       </c>
       <c r="C16" t="n">
-        <v>37.66325758925294</v>
+        <v>34.78379555008524</v>
       </c>
       <c r="D16" t="n">
-        <v>1.418130131471045</v>
+        <v>1.265290453675149</v>
       </c>
       <c r="E16" t="n">
-        <v>11.94243886056539</v>
+        <v>11.33786879512668</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568061269692774</v>
+        <v>0.7570013335079759</v>
       </c>
       <c r="G16" t="n">
-        <v>23.576895356328</v>
+        <v>21.45281457585413</v>
       </c>
       <c r="H16" t="n">
-        <v>36.59597687336524</v>
+        <v>36.8959631065152</v>
       </c>
       <c r="I16" t="n">
-        <v>2.001461129654591</v>
+        <v>1.973399951797289</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730038293557984</v>
+        <v>4.731258334424849</v>
       </c>
       <c r="K16" t="n">
-        <v>18.97825322808847</v>
+        <v>21.58640344909872</v>
       </c>
       <c r="L16" t="n">
-        <v>43.29182870160891</v>
+        <v>43.56407613803138</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93333951895033</v>
+        <v>99.93427513721535</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.73812646576918</v>
+        <v>80.38807771620542</v>
       </c>
       <c r="C17" t="n">
-        <v>38.93020541829704</v>
+        <v>36.2167591132793</v>
       </c>
       <c r="D17" t="n">
-        <v>1.419251996289952</v>
+        <v>1.26630867239598</v>
       </c>
       <c r="E17" t="n">
-        <v>12.7339754253716</v>
+        <v>12.21117653207681</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574048267287271</v>
+        <v>0.7576105161088824</v>
       </c>
       <c r="G17" t="n">
-        <v>24.05037036325481</v>
+        <v>22.01080814916826</v>
       </c>
       <c r="H17" t="n">
-        <v>37.07975111109205</v>
+        <v>37.46638426346976</v>
       </c>
       <c r="I17" t="n">
-        <v>1.963592575977504</v>
+        <v>1.940723857305217</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733780167054544</v>
+        <v>4.735065725680514</v>
       </c>
       <c r="K17" t="n">
-        <v>17.26187353423082</v>
+        <v>19.61192228379458</v>
       </c>
       <c r="L17" t="n">
-        <v>43.74251969978557</v>
+        <v>44.10667982452512</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93459865231343</v>
+        <v>99.93536122159901</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.46733420836927</v>
+        <v>77.7682348800376</v>
       </c>
       <c r="C18" t="n">
-        <v>36.96293154535316</v>
+        <v>33.89560601376338</v>
       </c>
       <c r="D18" t="n">
-        <v>1.335798218860771</v>
+        <v>1.17363987226018</v>
       </c>
       <c r="E18" t="n">
-        <v>12.25810805737668</v>
+        <v>11.58729139542814</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579185767094778</v>
+        <v>0.7581360565654889</v>
       </c>
       <c r="G18" t="n">
-        <v>22.6361787604731</v>
+        <v>20.40005144689963</v>
       </c>
       <c r="H18" t="n">
-        <v>37.10490241822306</v>
+        <v>37.49237400394267</v>
       </c>
       <c r="I18" t="n">
-        <v>1.637437072291942</v>
+        <v>1.61839175140718</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736991104434236</v>
+        <v>4.738350353534305</v>
       </c>
       <c r="K18" t="n">
-        <v>19.53266579163073</v>
+        <v>22.2317651199624</v>
       </c>
       <c r="L18" t="n">
-        <v>43.44985842479451</v>
+        <v>43.81871987023796</v>
       </c>
       <c r="M18" t="n">
-        <v>99.9454557617784</v>
+        <v>99.94609100396374</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.59404999048766</v>
+        <v>76.7427503155666</v>
       </c>
       <c r="C19" t="n">
-        <v>36.3421412111345</v>
+        <v>33.10020105515471</v>
       </c>
       <c r="D19" t="n">
-        <v>1.304345724652405</v>
+        <v>1.137272202819739</v>
       </c>
       <c r="E19" t="n">
-        <v>12.19703242922158</v>
+        <v>11.45608401152245</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7583519401961225</v>
+        <v>0.7585862371325945</v>
       </c>
       <c r="G19" t="n">
-        <v>22.10319086506288</v>
+        <v>19.76791347585397</v>
       </c>
       <c r="H19" t="n">
-        <v>37.12611829863251</v>
+        <v>37.51463694480278</v>
       </c>
       <c r="I19" t="n">
-        <v>1.365311106496378</v>
+        <v>1.367093461356353</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739699626225765</v>
+        <v>4.741163982078715</v>
       </c>
       <c r="K19" t="n">
-        <v>20.40595000951236</v>
+        <v>23.25724968443341</v>
       </c>
       <c r="L19" t="n">
-        <v>43.20642441623392</v>
+        <v>43.59700652160753</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95451563688077</v>
+        <v>99.95445726119564</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.16871100948519</v>
+        <v>74.06261835288095</v>
       </c>
       <c r="C20" t="n">
-        <v>34.12720852069948</v>
+        <v>30.62959805649817</v>
       </c>
       <c r="D20" t="n">
-        <v>1.216092975981698</v>
+        <v>1.043619421537372</v>
       </c>
       <c r="E20" t="n">
-        <v>11.56149429308389</v>
+        <v>10.70266295324072</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587248228399668</v>
+        <v>0.7589753936782848</v>
       </c>
       <c r="G20" t="n">
-        <v>20.6076768219936</v>
+        <v>18.1400533447677</v>
       </c>
       <c r="H20" t="n">
-        <v>37.14437325970413</v>
+        <v>37.53388204287027</v>
       </c>
       <c r="I20" t="n">
-        <v>1.138318693132114</v>
+        <v>1.139828986297336</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742030142749792</v>
+        <v>4.743596210489279</v>
       </c>
       <c r="K20" t="n">
-        <v>22.8312889905148</v>
+        <v>25.93738164711903</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00357718027193</v>
+        <v>43.3950454780118</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96207469148622</v>
+        <v>99.962025181629</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.83688046733937</v>
+        <v>80.60601588907114</v>
       </c>
       <c r="C21" t="n">
-        <v>37.64710360091489</v>
+        <v>34.81871845935913</v>
       </c>
       <c r="D21" t="n">
-        <v>1.216892854446609</v>
+        <v>1.044266324450847</v>
       </c>
       <c r="E21" t="n">
-        <v>13.45802197911798</v>
+        <v>12.92220637801916</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592238699182486</v>
+        <v>0.7594458557866874</v>
       </c>
       <c r="G21" t="n">
-        <v>22.23772707271912</v>
+        <v>20.11438279803784</v>
       </c>
       <c r="H21" t="n">
-        <v>38.78530043153892</v>
+        <v>39.5202330473202</v>
       </c>
       <c r="I21" t="n">
-        <v>1.634565072609444</v>
+        <v>1.498944886789621</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745149186989054</v>
+        <v>4.746536598666796</v>
       </c>
       <c r="K21" t="n">
-        <v>17.16311953266063</v>
+        <v>19.39398411092883</v>
       </c>
       <c r="L21" t="n">
-        <v>45.13532717798718</v>
+        <v>45.73736355240379</v>
       </c>
       <c r="M21" t="n">
-        <v>99.9455503115627</v>
+        <v>99.95006612269175</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_6_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.4484642750741</v>
+        <v>45.44932673138716</v>
       </c>
       <c r="M2" t="n">
-        <v>99.79120636112299</v>
+        <v>99.71854766707511</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.98504916991385</v>
+        <v>88.04990342325638</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93464719069895</v>
+        <v>45.93171565114792</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228617637406825</v>
+        <v>2.228786263183946</v>
       </c>
       <c r="E3" t="n">
-        <v>5.707339354876392</v>
+        <v>5.709340666176781</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428725458022749</v>
+        <v>0.7429287543946487</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97565583576932</v>
+        <v>33.97393468614026</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17213710690464</v>
+        <v>34.17472270215384</v>
       </c>
       <c r="I3" t="n">
-        <v>6.515473277890184</v>
+        <v>6.576885636240356</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642953411264218</v>
+        <v>4.643304714966554</v>
       </c>
       <c r="K3" t="n">
-        <v>12.01495083008616</v>
+        <v>11.95009657674361</v>
       </c>
       <c r="L3" t="n">
-        <v>48.8165180444015</v>
+        <v>48.88211719881465</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7661160651866</v>
+        <v>106.7639294267062</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.03374953111587</v>
+        <v>87.12905559876056</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60811257920824</v>
+        <v>42.64759888376655</v>
       </c>
       <c r="D4" t="n">
-        <v>2.182571638735644</v>
+        <v>2.184397932988956</v>
       </c>
       <c r="E4" t="n">
-        <v>6.496231207189331</v>
+        <v>6.51100957921193</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444205571176626</v>
+        <v>0.7444897925930314</v>
       </c>
       <c r="G4" t="n">
-        <v>33.27367673571755</v>
+        <v>33.29731250132966</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24334562741247</v>
+        <v>34.24653045927944</v>
       </c>
       <c r="I4" t="n">
-        <v>5.440875282957815</v>
+        <v>5.492254129651102</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652628481985391</v>
+        <v>4.653061203706446</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96625046888413</v>
+        <v>12.87094440123942</v>
       </c>
       <c r="L4" t="n">
-        <v>44.24465158307734</v>
+        <v>44.29876544732069</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81901463116971</v>
+        <v>99.81730873232667</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.65858973049203</v>
+        <v>86.10260143414122</v>
       </c>
       <c r="C5" t="n">
-        <v>42.07741746076939</v>
+        <v>42.47356871506689</v>
       </c>
       <c r="D5" t="n">
-        <v>2.114760419124912</v>
+        <v>2.134785899194319</v>
       </c>
       <c r="E5" t="n">
-        <v>7.051409907750909</v>
+        <v>7.127298643862827</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7457363291499316</v>
+        <v>0.7458112731990308</v>
       </c>
       <c r="G5" t="n">
-        <v>32.23988313172417</v>
+        <v>32.54106412362396</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30387114089685</v>
+        <v>34.30731856715542</v>
       </c>
       <c r="I5" t="n">
-        <v>4.54207674465819</v>
+        <v>4.585002469611725</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660852057187072</v>
+        <v>4.661320457493943</v>
       </c>
       <c r="K5" t="n">
-        <v>14.34141026950796</v>
+        <v>13.89739856585876</v>
       </c>
       <c r="L5" t="n">
-        <v>43.43003684519604</v>
+        <v>43.47647010436181</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8488645754734</v>
+        <v>99.84743738528746</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.0324732043197</v>
+        <v>84.87709544083573</v>
       </c>
       <c r="C6" t="n">
-        <v>41.15651725389122</v>
+        <v>41.96025984513182</v>
       </c>
       <c r="D6" t="n">
-        <v>2.034763682238788</v>
+        <v>2.075316354144757</v>
       </c>
       <c r="E6" t="n">
-        <v>7.416463159096177</v>
+        <v>7.56651365207202</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468576829896115</v>
+        <v>0.7469320720360403</v>
       </c>
       <c r="G6" t="n">
-        <v>31.02031923937784</v>
+        <v>31.63455528843309</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35545341752212</v>
+        <v>34.35887531365785</v>
       </c>
       <c r="I6" t="n">
-        <v>3.79075550441009</v>
+        <v>3.826577310266712</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667860518685072</v>
+        <v>4.668325450225252</v>
       </c>
       <c r="K6" t="n">
-        <v>15.9675267956803</v>
+        <v>15.12290455916427</v>
       </c>
       <c r="L6" t="n">
-        <v>42.74978715196574</v>
+        <v>42.78947441599247</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87383120153726</v>
+        <v>99.87263882028854</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.17583162147088</v>
+        <v>83.46204492321728</v>
       </c>
       <c r="C7" t="n">
-        <v>39.88825600091057</v>
+        <v>41.13973591993783</v>
       </c>
       <c r="D7" t="n">
-        <v>1.943909318942483</v>
+        <v>2.006725363854241</v>
       </c>
       <c r="E7" t="n">
-        <v>7.612479514498316</v>
+        <v>7.848580659668903</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478159220575581</v>
+        <v>0.7478845469140099</v>
       </c>
       <c r="G7" t="n">
-        <v>29.63522898130872</v>
+        <v>30.58900603021992</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39953241464766</v>
+        <v>34.40268915804445</v>
       </c>
       <c r="I7" t="n">
-        <v>3.163015957156398</v>
+        <v>3.192880746303175</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673849512859737</v>
+        <v>4.674278418212562</v>
       </c>
       <c r="K7" t="n">
-        <v>17.82416837852911</v>
+        <v>16.53795507678272</v>
       </c>
       <c r="L7" t="n">
-        <v>42.18227685654894</v>
+        <v>42.21601518910537</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89470123598862</v>
+        <v>99.89370618582593</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.19521770944549</v>
+        <v>88.43215637244857</v>
       </c>
       <c r="C8" t="n">
-        <v>42.24005463977129</v>
+        <v>43.48696825770126</v>
       </c>
       <c r="D8" t="n">
-        <v>1.948148447106641</v>
+        <v>2.011030165083159</v>
       </c>
       <c r="E8" t="n">
-        <v>9.483086563477228</v>
+        <v>9.714719439310084</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494467015933675</v>
+        <v>0.7494888991460761</v>
       </c>
       <c r="G8" t="n">
-        <v>30.15148679501277</v>
+        <v>31.10501743456385</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47454827329489</v>
+        <v>34.4764893607195</v>
       </c>
       <c r="I8" t="n">
-        <v>5.704459044002043</v>
+        <v>5.69110545396294</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684041884958546</v>
+        <v>4.684305619662976</v>
       </c>
       <c r="K8" t="n">
-        <v>12.80478229055452</v>
+        <v>11.56784362755141</v>
       </c>
       <c r="L8" t="n">
-        <v>44.76542819412041</v>
+        <v>44.75589067802181</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81026512444622</v>
+        <v>99.81070256327449</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.01893920736295</v>
+        <v>86.54973715620896</v>
       </c>
       <c r="C9" t="n">
-        <v>40.94817598344109</v>
+        <v>42.48826803491397</v>
       </c>
       <c r="D9" t="n">
-        <v>1.849637237474758</v>
+        <v>1.926163268134449</v>
       </c>
       <c r="E9" t="n">
-        <v>9.79732467013973</v>
+        <v>10.096629106779</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508461188464982</v>
+        <v>0.7508603730988042</v>
       </c>
       <c r="G9" t="n">
-        <v>28.62682914339087</v>
+        <v>29.79236367379951</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53892146693891</v>
+        <v>34.53957716254499</v>
       </c>
       <c r="I9" t="n">
-        <v>4.76259232778158</v>
+        <v>4.751266239984693</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692788242790614</v>
+        <v>4.692877331867527</v>
       </c>
       <c r="K9" t="n">
-        <v>14.98106079263704</v>
+        <v>13.45026284379102</v>
       </c>
       <c r="L9" t="n">
-        <v>43.91230602825514</v>
+        <v>43.90338285868493</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84154280433327</v>
+        <v>99.84191373738992</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>82.61144664281649</v>
+        <v>84.56044722895382</v>
       </c>
       <c r="C10" t="n">
-        <v>39.27861576194174</v>
+        <v>41.23662458344336</v>
       </c>
       <c r="D10" t="n">
-        <v>1.741858770633973</v>
+        <v>1.83739685489075</v>
       </c>
       <c r="E10" t="n">
-        <v>9.888966143059895</v>
+        <v>10.29225990745913</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520504548178754</v>
+        <v>0.7520341272583863</v>
       </c>
       <c r="G10" t="n">
-        <v>26.95874218391761</v>
+        <v>28.41939529197775</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59432092162226</v>
+        <v>34.59356985388576</v>
       </c>
       <c r="I10" t="n">
-        <v>3.975192826153171</v>
+        <v>3.965577898117133</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700315342611721</v>
+        <v>4.700213295364915</v>
       </c>
       <c r="K10" t="n">
-        <v>17.3885533571835</v>
+        <v>15.43955277104618</v>
       </c>
       <c r="L10" t="n">
-        <v>43.2005366495475</v>
+        <v>43.19184302773309</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86770576867274</v>
+        <v>99.86802038222262</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.05574644144352</v>
+        <v>82.3750105690534</v>
       </c>
       <c r="C11" t="n">
-        <v>37.33802746579985</v>
+        <v>39.66642422975742</v>
       </c>
       <c r="D11" t="n">
-        <v>1.628745935778692</v>
+        <v>1.740696013423776</v>
       </c>
       <c r="E11" t="n">
-        <v>9.799669102720124</v>
+        <v>10.30209806945958</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530892014010498</v>
+        <v>0.7530411219798663</v>
       </c>
       <c r="G11" t="n">
-        <v>25.20809522908688</v>
+        <v>26.92370347591649</v>
       </c>
       <c r="H11" t="n">
-        <v>34.64210326444828</v>
+        <v>34.63989161107384</v>
       </c>
       <c r="I11" t="n">
-        <v>3.317236199251921</v>
+        <v>3.309073264825679</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706807508756562</v>
+        <v>4.706507012374164</v>
       </c>
       <c r="K11" t="n">
-        <v>19.94425355855649</v>
+        <v>17.6249894309466</v>
       </c>
       <c r="L11" t="n">
-        <v>42.60729695269495</v>
+        <v>42.59843139768162</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88957797705129</v>
+        <v>99.88984505838565</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>77.40362058515039</v>
+        <v>80.01727096761718</v>
       </c>
       <c r="C12" t="n">
-        <v>35.19820086258973</v>
+        <v>37.82139258834707</v>
       </c>
       <c r="D12" t="n">
-        <v>1.512641352751869</v>
+        <v>1.637252770498289</v>
       </c>
       <c r="E12" t="n">
-        <v>9.562379504504234</v>
+        <v>10.15000385984786</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539867879910905</v>
+        <v>0.7539071621082192</v>
       </c>
       <c r="G12" t="n">
-        <v>23.41114499812632</v>
+        <v>25.32372554890611</v>
       </c>
       <c r="H12" t="n">
-        <v>34.68339224759015</v>
+        <v>34.67972945697807</v>
       </c>
       <c r="I12" t="n">
-        <v>2.767658269242405</v>
+        <v>2.760732406102261</v>
       </c>
       <c r="J12" t="n">
-        <v>4.712417424944316</v>
+        <v>4.71191976317637</v>
       </c>
       <c r="K12" t="n">
-        <v>22.59637941484961</v>
+        <v>19.98272903238281</v>
       </c>
       <c r="L12" t="n">
-        <v>42.11327427258144</v>
+        <v>42.1039596774694</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90785455002079</v>
+        <v>99.90808129819929</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>74.78376265279829</v>
+        <v>77.63442395288678</v>
       </c>
       <c r="C13" t="n">
-        <v>33.00469169286063</v>
+        <v>35.86547738303318</v>
       </c>
       <c r="D13" t="n">
-        <v>1.399166824399931</v>
+        <v>1.533641864582485</v>
       </c>
       <c r="E13" t="n">
-        <v>9.229826537527092</v>
+        <v>9.891491391859281</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754762701087761</v>
+        <v>0.7546526053009294</v>
       </c>
       <c r="G13" t="n">
-        <v>21.65490011429563</v>
+        <v>23.72115434391936</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71908425003699</v>
+        <v>34.71401984384274</v>
       </c>
       <c r="I13" t="n">
-        <v>2.308755343652386</v>
+        <v>2.30288512025118</v>
       </c>
       <c r="J13" t="n">
-        <v>4.717266881798506</v>
+        <v>4.716578783130809</v>
       </c>
       <c r="K13" t="n">
-        <v>25.21623734720172</v>
+        <v>22.36557604711321</v>
       </c>
       <c r="L13" t="n">
-        <v>41.7021915635698</v>
+        <v>41.69225955857299</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92312060363214</v>
+        <v>99.92331298871939</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>82.07826438131377</v>
+        <v>84.12273434045368</v>
       </c>
       <c r="C14" t="n">
-        <v>37.64640906283169</v>
+        <v>39.78219682434178</v>
       </c>
       <c r="D14" t="n">
-        <v>1.400778625612142</v>
+        <v>1.53554364139971</v>
       </c>
       <c r="E14" t="n">
-        <v>11.78336917120792</v>
+        <v>12.10758082783372</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7556321666978155</v>
+        <v>0.7555884045008359</v>
       </c>
       <c r="G14" t="n">
-        <v>23.74999671402901</v>
+        <v>25.4328154545303</v>
       </c>
       <c r="H14" t="n">
-        <v>36.82923042603199</v>
+        <v>36.43931254423055</v>
       </c>
       <c r="I14" t="n">
-        <v>2.836556235873558</v>
+        <v>3.129465939828332</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722701041861346</v>
+        <v>4.722427528130225</v>
       </c>
       <c r="K14" t="n">
-        <v>17.92173561868623</v>
+        <v>15.87726565954633</v>
       </c>
       <c r="L14" t="n">
-        <v>44.33741223974925</v>
+        <v>44.2363511799786</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90555692126716</v>
+        <v>99.8958136638667</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>81.12109963958127</v>
+        <v>83.40633340571068</v>
       </c>
       <c r="C15" t="n">
-        <v>37.12657807968575</v>
+        <v>39.54977544071996</v>
       </c>
       <c r="D15" t="n">
-        <v>1.365803436047258</v>
+        <v>1.508964372495522</v>
       </c>
       <c r="E15" t="n">
-        <v>11.88350656959434</v>
+        <v>12.33310795020857</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563668286394191</v>
+        <v>0.7563767323321415</v>
       </c>
       <c r="G15" t="n">
-        <v>23.15699749056104</v>
+        <v>24.99258984144362</v>
       </c>
       <c r="H15" t="n">
-        <v>36.86503757549573</v>
+        <v>36.47733076163721</v>
       </c>
       <c r="I15" t="n">
-        <v>2.366095060247138</v>
+        <v>2.610609170517727</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727292678996369</v>
+        <v>4.727354577075885</v>
       </c>
       <c r="K15" t="n">
-        <v>18.8789003604187</v>
+        <v>16.59366659428931</v>
       </c>
       <c r="L15" t="n">
-        <v>43.91572833112131</v>
+        <v>43.76962835555106</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92120677122576</v>
+        <v>99.91307039056034</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>78.41359655090127</v>
+        <v>81.05614721146833</v>
       </c>
       <c r="C16" t="n">
-        <v>34.78379555008524</v>
+        <v>37.60343730925386</v>
       </c>
       <c r="D16" t="n">
-        <v>1.265290453675149</v>
+        <v>1.418914683621162</v>
       </c>
       <c r="E16" t="n">
-        <v>11.33786879512668</v>
+        <v>11.9600207096791</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570013335079759</v>
+        <v>0.7570540310881164</v>
       </c>
       <c r="G16" t="n">
-        <v>21.45281457585413</v>
+        <v>23.50111994300958</v>
       </c>
       <c r="H16" t="n">
-        <v>36.8959631065152</v>
+        <v>36.50999444587028</v>
       </c>
       <c r="I16" t="n">
-        <v>1.973399951797289</v>
+        <v>2.177455703899351</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731258334424849</v>
+        <v>4.731587694300727</v>
       </c>
       <c r="K16" t="n">
-        <v>21.58640344909872</v>
+        <v>18.94385278853166</v>
       </c>
       <c r="L16" t="n">
-        <v>43.56407613803138</v>
+        <v>43.3801929808112</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93427513721535</v>
+        <v>99.92748307859674</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>80.38807771620542</v>
+        <v>82.70189997548248</v>
       </c>
       <c r="C17" t="n">
-        <v>36.2167591132793</v>
+        <v>38.79077529826934</v>
       </c>
       <c r="D17" t="n">
-        <v>1.26630867239598</v>
+        <v>1.420175612711578</v>
       </c>
       <c r="E17" t="n">
-        <v>12.21117653207681</v>
+        <v>12.73172879020967</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7576105161088824</v>
+        <v>0.7577267927853731</v>
       </c>
       <c r="G17" t="n">
-        <v>22.01080814916826</v>
+        <v>23.91561581363736</v>
       </c>
       <c r="H17" t="n">
-        <v>37.46638426346976</v>
+        <v>36.93605074961188</v>
       </c>
       <c r="I17" t="n">
-        <v>1.940723857305217</v>
+        <v>2.20480976161803</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735065725680514</v>
+        <v>4.735792454908582</v>
       </c>
       <c r="K17" t="n">
-        <v>19.61192228379458</v>
+        <v>17.29810002451752</v>
       </c>
       <c r="L17" t="n">
-        <v>44.10667982452512</v>
+        <v>43.83769627119185</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93536122159901</v>
+        <v>99.92657159397871</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>77.7682348800376</v>
+        <v>80.47614048527636</v>
       </c>
       <c r="C18" t="n">
-        <v>33.89560601376338</v>
+        <v>36.90571109714038</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17363987226018</v>
+        <v>1.338158128701148</v>
       </c>
       <c r="E18" t="n">
-        <v>11.58729139542814</v>
+        <v>12.30290725407444</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7581360565654889</v>
+        <v>0.7583038843985979</v>
       </c>
       <c r="G18" t="n">
-        <v>20.40005144689963</v>
+        <v>22.53444955501569</v>
       </c>
       <c r="H18" t="n">
-        <v>37.49237400394267</v>
+        <v>36.96418158161649</v>
       </c>
       <c r="I18" t="n">
-        <v>1.61839175140718</v>
+        <v>1.838740803978749</v>
       </c>
       <c r="J18" t="n">
-        <v>4.738350353534305</v>
+        <v>4.739399277491236</v>
       </c>
       <c r="K18" t="n">
-        <v>22.2317651199624</v>
+        <v>19.52385951472364</v>
       </c>
       <c r="L18" t="n">
-        <v>43.81871987023796</v>
+        <v>43.50918467253549</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94609100396374</v>
+        <v>99.93875528439951</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>76.7427503155666</v>
+        <v>79.62836207275105</v>
       </c>
       <c r="C19" t="n">
-        <v>33.10020105515471</v>
+        <v>36.34142107688385</v>
       </c>
       <c r="D19" t="n">
-        <v>1.137272202819739</v>
+        <v>1.307636959298137</v>
       </c>
       <c r="E19" t="n">
-        <v>11.45608401152245</v>
+        <v>12.27784290876728</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7585862371325945</v>
+        <v>0.7587905965292436</v>
       </c>
       <c r="G19" t="n">
-        <v>19.76791347585397</v>
+        <v>22.02047610335806</v>
       </c>
       <c r="H19" t="n">
-        <v>37.51463694480278</v>
+        <v>36.98790678723038</v>
       </c>
       <c r="I19" t="n">
-        <v>1.367093461356353</v>
+        <v>1.53326748926018</v>
       </c>
       <c r="J19" t="n">
-        <v>4.741163982078715</v>
+        <v>4.742441228307772</v>
       </c>
       <c r="K19" t="n">
-        <v>23.25724968443341</v>
+        <v>20.37163792724893</v>
       </c>
       <c r="L19" t="n">
-        <v>43.59700652160753</v>
+        <v>43.23586486242336</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95445726119564</v>
+        <v>99.94892386655614</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>74.06261835288095</v>
+        <v>77.17399281213406</v>
       </c>
       <c r="C20" t="n">
-        <v>30.62959805649817</v>
+        <v>34.12333112528849</v>
       </c>
       <c r="D20" t="n">
-        <v>1.043619421537372</v>
+        <v>1.218171965590591</v>
       </c>
       <c r="E20" t="n">
-        <v>10.70266295324072</v>
+        <v>11.65089742133239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7589753936782848</v>
+        <v>0.7592095889247299</v>
       </c>
       <c r="G20" t="n">
-        <v>18.1400533447677</v>
+        <v>20.51389452349702</v>
       </c>
       <c r="H20" t="n">
-        <v>37.53388204287027</v>
+        <v>37.00833093552596</v>
       </c>
       <c r="I20" t="n">
-        <v>1.139828986297336</v>
+        <v>1.278428446483798</v>
       </c>
       <c r="J20" t="n">
-        <v>4.743596210489279</v>
+        <v>4.745059930779561</v>
       </c>
       <c r="K20" t="n">
-        <v>25.93738164711903</v>
+        <v>22.82600718786596</v>
       </c>
       <c r="L20" t="n">
-        <v>43.3950454780118</v>
+        <v>43.00807092325496</v>
       </c>
       <c r="M20" t="n">
-        <v>99.962025181629</v>
+        <v>99.95740923640942</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>80.60601588907114</v>
+        <v>82.86942540373514</v>
       </c>
       <c r="C21" t="n">
-        <v>34.81871845935913</v>
+        <v>37.56977087434019</v>
       </c>
       <c r="D21" t="n">
-        <v>1.044266324450847</v>
+        <v>1.219117858975765</v>
       </c>
       <c r="E21" t="n">
-        <v>12.92220637801916</v>
+        <v>13.53594096328655</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7594458557866874</v>
+        <v>0.7597991044844447</v>
       </c>
       <c r="G21" t="n">
-        <v>20.11438279803784</v>
+        <v>22.08408534587242</v>
       </c>
       <c r="H21" t="n">
-        <v>39.5202330473202</v>
+        <v>38.59132945561154</v>
       </c>
       <c r="I21" t="n">
-        <v>1.498944886789621</v>
+        <v>1.930408272476645</v>
       </c>
       <c r="J21" t="n">
-        <v>4.746536598666796</v>
+        <v>4.748744403027779</v>
       </c>
       <c r="K21" t="n">
-        <v>19.39398411092883</v>
+        <v>17.13057459626485</v>
       </c>
       <c r="L21" t="n">
-        <v>45.73736355240379</v>
+        <v>45.23535751270754</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95006612269175</v>
+        <v>99.93570298331258</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_6_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_6_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.44932673138716</v>
+        <v>44.13090890747409</v>
       </c>
       <c r="M2" t="n">
-        <v>99.71854766707511</v>
+        <v>94.59935306763487</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.04990342325638</v>
+        <v>81.49533755066568</v>
       </c>
       <c r="C3" t="n">
-        <v>45.93171565114792</v>
+        <v>43.25089310622125</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228786263183946</v>
+        <v>2.181453717351702</v>
       </c>
       <c r="E3" t="n">
-        <v>5.709340666176781</v>
+        <v>4.148010353958095</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429287543946487</v>
+        <v>0.7376459880555708</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97393468614026</v>
+        <v>32.81269966516519</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17472270215384</v>
+        <v>33.93171545055625</v>
       </c>
       <c r="I3" t="n">
-        <v>6.576885636240356</v>
+        <v>3.073524950231545</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643304714966554</v>
+        <v>4.610287425347318</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95009657674361</v>
+        <v>18.50466244933431</v>
       </c>
       <c r="L3" t="n">
-        <v>48.88211719881465</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7639294267062</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.12905559876056</v>
+        <v>88.59467741295154</v>
       </c>
       <c r="C4" t="n">
-        <v>42.64759888376655</v>
+        <v>42.87982962827083</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184397932988956</v>
+        <v>2.187165923159493</v>
       </c>
       <c r="E4" t="n">
-        <v>6.51100957921193</v>
+        <v>6.550769043456135</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444897925930314</v>
+        <v>0.7395775374914121</v>
       </c>
       <c r="G4" t="n">
-        <v>33.29731250132966</v>
+        <v>33.5145993192392</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24653045927944</v>
+        <v>34.02056672460495</v>
       </c>
       <c r="I4" t="n">
-        <v>5.492254129651102</v>
+        <v>6.959639255679028</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653061203706446</v>
+        <v>4.622359609321325</v>
       </c>
       <c r="K4" t="n">
-        <v>12.87094440123942</v>
+        <v>11.40532258704844</v>
       </c>
       <c r="L4" t="n">
-        <v>44.29876544732069</v>
+        <v>45.4834656908492</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81730873232667</v>
+        <v>99.76861790616847</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.10260143414122</v>
+        <v>87.46467829709641</v>
       </c>
       <c r="C5" t="n">
-        <v>42.47356871506689</v>
+        <v>42.82872927077983</v>
       </c>
       <c r="D5" t="n">
-        <v>2.134785899194319</v>
+        <v>2.133387926066064</v>
       </c>
       <c r="E5" t="n">
-        <v>7.127298643862827</v>
+        <v>7.358456660064967</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458112731990308</v>
+        <v>0.741215848017708</v>
       </c>
       <c r="G5" t="n">
-        <v>32.54106412362396</v>
+        <v>32.69054294304352</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30731856715542</v>
+        <v>34.09592900881457</v>
       </c>
       <c r="I5" t="n">
-        <v>4.585002469611725</v>
+        <v>5.812546860978907</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661320457493943</v>
+        <v>4.632599050110675</v>
       </c>
       <c r="K5" t="n">
-        <v>13.89739856585876</v>
+        <v>12.5353217029036</v>
       </c>
       <c r="L5" t="n">
-        <v>43.47647010436181</v>
+        <v>44.4426257136588</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84743738528746</v>
+        <v>99.80667668734223</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.87709544083573</v>
+        <v>86.02363965262647</v>
       </c>
       <c r="C6" t="n">
-        <v>41.96025984513182</v>
+        <v>42.28986290785826</v>
       </c>
       <c r="D6" t="n">
-        <v>2.075316354144757</v>
+        <v>2.064381612016515</v>
       </c>
       <c r="E6" t="n">
-        <v>7.56651365207202</v>
+        <v>7.929257149384787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469320720360403</v>
+        <v>0.7426096682104028</v>
       </c>
       <c r="G6" t="n">
-        <v>31.63455528843309</v>
+        <v>31.63313849952175</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35887531365785</v>
+        <v>34.16004473767853</v>
       </c>
       <c r="I6" t="n">
-        <v>3.826577310266712</v>
+        <v>4.852897559499477</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668325450225252</v>
+        <v>4.641310426315017</v>
       </c>
       <c r="K6" t="n">
-        <v>15.12290455916427</v>
+        <v>13.97636034737354</v>
       </c>
       <c r="L6" t="n">
-        <v>42.78947441599247</v>
+        <v>43.572317109741</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87263882028854</v>
+        <v>99.8385403649728</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.46204492321728</v>
+        <v>84.39595833188143</v>
       </c>
       <c r="C7" t="n">
-        <v>41.13973591993783</v>
+        <v>41.41571915831893</v>
       </c>
       <c r="D7" t="n">
-        <v>2.006725363854241</v>
+        <v>1.986834105341704</v>
       </c>
       <c r="E7" t="n">
-        <v>7.848580659668903</v>
+        <v>8.306490252202471</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478845469140099</v>
+        <v>0.7437977102565601</v>
       </c>
       <c r="G7" t="n">
-        <v>30.58900603021992</v>
+        <v>30.44485480010404</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40268915804445</v>
+        <v>34.21469467180176</v>
       </c>
       <c r="I7" t="n">
-        <v>3.192880746303175</v>
+        <v>4.050551103071399</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674278418212562</v>
+        <v>4.6487356891035</v>
       </c>
       <c r="K7" t="n">
-        <v>16.53795507678272</v>
+        <v>15.60404166811855</v>
       </c>
       <c r="L7" t="n">
-        <v>42.21601518910537</v>
+        <v>42.84543646357644</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89370618582593</v>
+        <v>99.86519729001392</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.43215637244857</v>
+        <v>82.55403991732804</v>
       </c>
       <c r="C8" t="n">
-        <v>43.48696825770126</v>
+        <v>40.2026349954446</v>
       </c>
       <c r="D8" t="n">
-        <v>2.011030165083159</v>
+        <v>1.899591255658763</v>
       </c>
       <c r="E8" t="n">
-        <v>9.714719439310084</v>
+        <v>8.505092575001227</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494888991460761</v>
+        <v>0.7448128373926437</v>
       </c>
       <c r="G8" t="n">
-        <v>31.10501743456385</v>
+        <v>29.10800645237163</v>
       </c>
       <c r="H8" t="n">
-        <v>34.4764893607195</v>
+        <v>34.26139052006161</v>
       </c>
       <c r="I8" t="n">
-        <v>5.69110545396294</v>
+        <v>3.380066043138131</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684305619662976</v>
+        <v>4.655080233704023</v>
       </c>
       <c r="K8" t="n">
-        <v>11.56784362755141</v>
+        <v>17.44596008267198</v>
       </c>
       <c r="L8" t="n">
-        <v>44.75589067802181</v>
+        <v>42.23888961346476</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81070256327449</v>
+        <v>99.88748469158134</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.54973715620896</v>
+        <v>80.58286714080387</v>
       </c>
       <c r="C9" t="n">
-        <v>42.48826803491397</v>
+        <v>38.75578396100264</v>
       </c>
       <c r="D9" t="n">
-        <v>1.926163268134449</v>
+        <v>1.806931530228816</v>
       </c>
       <c r="E9" t="n">
-        <v>10.096629106779</v>
+        <v>8.560225855010394</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508603730988042</v>
+        <v>0.7456816646436332</v>
       </c>
       <c r="G9" t="n">
-        <v>29.79236367379951</v>
+        <v>27.68815369317658</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53957716254499</v>
+        <v>34.30135657360712</v>
       </c>
       <c r="I9" t="n">
-        <v>4.751266239984693</v>
+        <v>2.820007420114626</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692877331867527</v>
+        <v>4.660510404022707</v>
       </c>
       <c r="K9" t="n">
-        <v>13.45026284379102</v>
+        <v>19.41713285919612</v>
       </c>
       <c r="L9" t="n">
-        <v>43.90338285868493</v>
+        <v>41.73319245638075</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84191373738992</v>
+        <v>99.9061092765795</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>84.56044722895382</v>
+        <v>85.62332588891786</v>
       </c>
       <c r="C10" t="n">
-        <v>41.23662458344336</v>
+        <v>42.17375883185237</v>
       </c>
       <c r="D10" t="n">
-        <v>1.83739685489075</v>
+        <v>1.809008192356236</v>
       </c>
       <c r="E10" t="n">
-        <v>10.29225990745913</v>
+        <v>10.50439705135756</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520341272583863</v>
+        <v>0.746538658307295</v>
       </c>
       <c r="G10" t="n">
-        <v>28.41939529197775</v>
+        <v>29.16228419735575</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59356985388576</v>
+        <v>35.78308746979505</v>
       </c>
       <c r="I10" t="n">
-        <v>3.965577898117133</v>
+        <v>2.952143705325383</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700213295364915</v>
+        <v>4.665866614420594</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43955277104618</v>
+        <v>14.37667411108212</v>
       </c>
       <c r="L10" t="n">
-        <v>43.19184302773309</v>
+        <v>43.35127523127466</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86802038222262</v>
+        <v>99.90170817420916</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>82.3750105690534</v>
+        <v>85.1663910549303</v>
       </c>
       <c r="C11" t="n">
-        <v>39.66642422975742</v>
+        <v>42.05391275772432</v>
       </c>
       <c r="D11" t="n">
-        <v>1.740696013423776</v>
+        <v>1.779260981723221</v>
       </c>
       <c r="E11" t="n">
-        <v>10.30209806945958</v>
+        <v>10.81840370434096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530411219798663</v>
+        <v>0.7472734237906606</v>
       </c>
       <c r="G11" t="n">
-        <v>26.92370347591649</v>
+        <v>28.75036535575982</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63989161107384</v>
+        <v>35.88593006944965</v>
       </c>
       <c r="I11" t="n">
-        <v>3.309073264825679</v>
+        <v>2.514698621174368</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706507012374164</v>
+        <v>4.670458898691629</v>
       </c>
       <c r="K11" t="n">
-        <v>17.6249894309466</v>
+        <v>14.83360894506971</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59843139768162</v>
+        <v>43.02873743007793</v>
       </c>
       <c r="M11" t="n">
-        <v>99.88984505838565</v>
+        <v>99.91625913287196</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>80.01727096761718</v>
+        <v>83.08158108262289</v>
       </c>
       <c r="C12" t="n">
-        <v>37.82139258834707</v>
+        <v>40.35975719069258</v>
       </c>
       <c r="D12" t="n">
-        <v>1.637252770498289</v>
+        <v>1.690970545062966</v>
       </c>
       <c r="E12" t="n">
-        <v>10.15000385984786</v>
+        <v>10.63113078645842</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7539071621082192</v>
+        <v>0.747902239704171</v>
       </c>
       <c r="G12" t="n">
-        <v>25.32372554890611</v>
+        <v>27.3237155626848</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67972945697807</v>
+        <v>35.91612737498786</v>
       </c>
       <c r="I12" t="n">
-        <v>2.760732406102261</v>
+        <v>2.097345575573608</v>
       </c>
       <c r="J12" t="n">
-        <v>4.71191976317637</v>
+        <v>4.674388998151069</v>
       </c>
       <c r="K12" t="n">
-        <v>19.98272903238281</v>
+        <v>16.91841891737711</v>
       </c>
       <c r="L12" t="n">
-        <v>42.1039596774694</v>
+        <v>42.65197115245325</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90808129819929</v>
+        <v>99.93014726052294</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>77.63442395288678</v>
+        <v>84.24379364986433</v>
       </c>
       <c r="C13" t="n">
-        <v>35.86547738303318</v>
+        <v>41.32974011995833</v>
       </c>
       <c r="D13" t="n">
-        <v>1.533641864582485</v>
+        <v>1.692278389930631</v>
       </c>
       <c r="E13" t="n">
-        <v>9.891491391859281</v>
+        <v>11.27061705633643</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546526053009294</v>
+        <v>0.7484806886360985</v>
       </c>
       <c r="G13" t="n">
-        <v>23.72115434391936</v>
+        <v>27.65032958531689</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71401984384274</v>
+        <v>36.24938701408109</v>
       </c>
       <c r="I13" t="n">
-        <v>2.30288512025118</v>
+        <v>1.954696611587578</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716578783130809</v>
+        <v>4.678004303975616</v>
       </c>
       <c r="K13" t="n">
-        <v>22.36557604711321</v>
+        <v>15.75620635013566</v>
       </c>
       <c r="L13" t="n">
-        <v>41.69225955857299</v>
+        <v>42.84894733117818</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92331298871939</v>
+        <v>99.93489380127217</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>84.12273434045368</v>
+        <v>82.02236366703397</v>
       </c>
       <c r="C14" t="n">
-        <v>39.78219682434178</v>
+        <v>39.41176137788795</v>
       </c>
       <c r="D14" t="n">
-        <v>1.53554364139971</v>
+        <v>1.600775168710461</v>
       </c>
       <c r="E14" t="n">
-        <v>12.10758082783372</v>
+        <v>10.93286875656129</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7555884045008359</v>
+        <v>0.7489764957662044</v>
       </c>
       <c r="G14" t="n">
-        <v>25.4328154545303</v>
+        <v>26.15524801959439</v>
       </c>
       <c r="H14" t="n">
-        <v>36.43931254423055</v>
+        <v>36.27339926291587</v>
       </c>
       <c r="I14" t="n">
-        <v>3.129465939828332</v>
+        <v>1.629992864946987</v>
       </c>
       <c r="J14" t="n">
-        <v>4.722427528130225</v>
+        <v>4.681103098538778</v>
       </c>
       <c r="K14" t="n">
-        <v>15.87726565954633</v>
+        <v>17.97763633296604</v>
       </c>
       <c r="L14" t="n">
-        <v>44.2363511799786</v>
+        <v>42.55630516104635</v>
       </c>
       <c r="M14" t="n">
-        <v>99.8958136638667</v>
+        <v>99.94570287190034</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>83.40633340571068</v>
+        <v>80.97526101811545</v>
       </c>
       <c r="C15" t="n">
-        <v>39.54977544071996</v>
+        <v>38.57928440817798</v>
       </c>
       <c r="D15" t="n">
-        <v>1.508964372495522</v>
+        <v>1.556055554572853</v>
       </c>
       <c r="E15" t="n">
-        <v>12.33310795020857</v>
+        <v>10.86520727227597</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7563767323321415</v>
+        <v>0.7494050075433262</v>
       </c>
       <c r="G15" t="n">
-        <v>24.99258984144362</v>
+        <v>25.43068893228477</v>
       </c>
       <c r="H15" t="n">
-        <v>36.47733076163721</v>
+        <v>36.30027214330254</v>
       </c>
       <c r="I15" t="n">
-        <v>2.610609170517727</v>
+        <v>1.389850810990201</v>
       </c>
       <c r="J15" t="n">
-        <v>4.727354577075885</v>
+        <v>4.68378129714579</v>
       </c>
       <c r="K15" t="n">
-        <v>16.59366659428931</v>
+        <v>19.02473898188456</v>
       </c>
       <c r="L15" t="n">
-        <v>43.76962835555106</v>
+        <v>42.34967474025085</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91307039056034</v>
+        <v>99.9536981303134</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>81.05614721146833</v>
+        <v>78.3856560112384</v>
       </c>
       <c r="C16" t="n">
-        <v>37.60343730925386</v>
+        <v>36.20478659465965</v>
       </c>
       <c r="D16" t="n">
-        <v>1.418914683621162</v>
+        <v>1.450313822084518</v>
       </c>
       <c r="E16" t="n">
-        <v>11.9600207096791</v>
+        <v>10.31999222711845</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7570540310881164</v>
+        <v>0.7497742908121633</v>
       </c>
       <c r="G16" t="n">
-        <v>23.50111994300958</v>
+        <v>23.70254683724891</v>
       </c>
       <c r="H16" t="n">
-        <v>36.50999444587028</v>
+        <v>36.31815977818865</v>
       </c>
       <c r="I16" t="n">
-        <v>2.177455703899351</v>
+        <v>1.158779738209673</v>
       </c>
       <c r="J16" t="n">
-        <v>4.731587694300727</v>
+        <v>4.686089317576021</v>
       </c>
       <c r="K16" t="n">
-        <v>18.94385278853166</v>
+        <v>21.61434398876159</v>
       </c>
       <c r="L16" t="n">
-        <v>43.3801929808112</v>
+        <v>42.14226244960684</v>
       </c>
       <c r="M16" t="n">
-        <v>99.92748307859674</v>
+        <v>99.96139303302809</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.70189997548248</v>
+        <v>83.54328721045312</v>
       </c>
       <c r="C17" t="n">
-        <v>38.79077529826934</v>
+        <v>39.60088175263543</v>
       </c>
       <c r="D17" t="n">
-        <v>1.420175612711578</v>
+        <v>1.451075034737303</v>
       </c>
       <c r="E17" t="n">
-        <v>12.73172879020967</v>
+        <v>12.125044088757</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7577267927853731</v>
+        <v>0.7501678178324594</v>
       </c>
       <c r="G17" t="n">
-        <v>23.91561581363736</v>
+        <v>25.29537975577554</v>
       </c>
       <c r="H17" t="n">
-        <v>36.93605074961188</v>
+        <v>37.91761413550118</v>
       </c>
       <c r="I17" t="n">
-        <v>2.20480976161803</v>
+        <v>1.315457516396767</v>
       </c>
       <c r="J17" t="n">
-        <v>4.735792454908582</v>
+        <v>4.688548861452873</v>
       </c>
       <c r="K17" t="n">
-        <v>17.29810002451752</v>
+        <v>16.45671278954688</v>
       </c>
       <c r="L17" t="n">
-        <v>43.83769627119185</v>
+        <v>43.89857987626092</v>
       </c>
       <c r="M17" t="n">
-        <v>99.92657159397871</v>
+        <v>99.95617441844323</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>80.47614048527636</v>
+        <v>85.16894359896133</v>
       </c>
       <c r="C18" t="n">
-        <v>36.90571109714038</v>
+        <v>40.35827957043287</v>
       </c>
       <c r="D18" t="n">
-        <v>1.338158128701148</v>
+        <v>1.452287641521779</v>
       </c>
       <c r="E18" t="n">
-        <v>12.30290725407444</v>
+        <v>12.74528274096485</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7583038843985979</v>
+        <v>0.7507947038057019</v>
       </c>
       <c r="G18" t="n">
-        <v>22.53444955501569</v>
+        <v>25.44364032356672</v>
       </c>
       <c r="H18" t="n">
-        <v>36.96418158161649</v>
+        <v>37.94930040606001</v>
       </c>
       <c r="I18" t="n">
-        <v>1.838740803978749</v>
+        <v>2.135170884256621</v>
       </c>
       <c r="J18" t="n">
-        <v>4.739399277491236</v>
+        <v>4.692466898785638</v>
       </c>
       <c r="K18" t="n">
-        <v>19.52385951472364</v>
+        <v>14.83105640103867</v>
       </c>
       <c r="L18" t="n">
-        <v>43.50918467253549</v>
+        <v>44.73955109202605</v>
       </c>
       <c r="M18" t="n">
-        <v>99.93875528439951</v>
+        <v>99.9288870634976</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.62836207275105</v>
+        <v>82.25516550014201</v>
       </c>
       <c r="C19" t="n">
-        <v>36.34142107688385</v>
+        <v>37.77477882274204</v>
       </c>
       <c r="D19" t="n">
-        <v>1.307636959298137</v>
+        <v>1.34650994155172</v>
       </c>
       <c r="E19" t="n">
-        <v>12.27784290876728</v>
+        <v>12.11374267519647</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7587905965292436</v>
+        <v>0.7513364569241673</v>
       </c>
       <c r="G19" t="n">
-        <v>22.02047610335806</v>
+        <v>23.59044700611056</v>
       </c>
       <c r="H19" t="n">
-        <v>36.98790678723038</v>
+        <v>37.97668359314744</v>
       </c>
       <c r="I19" t="n">
-        <v>1.53326748926018</v>
+        <v>1.780592971435604</v>
       </c>
       <c r="J19" t="n">
-        <v>4.742441228307772</v>
+        <v>4.695852855776047</v>
       </c>
       <c r="K19" t="n">
-        <v>20.37163792724893</v>
+        <v>17.74483449985799</v>
       </c>
       <c r="L19" t="n">
-        <v>43.23586486242336</v>
+        <v>44.4210763750595</v>
       </c>
       <c r="M19" t="n">
-        <v>99.94892386655614</v>
+        <v>99.94068969765954</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>77.17399281213406</v>
+        <v>79.20062441548777</v>
       </c>
       <c r="C20" t="n">
-        <v>34.12333112528849</v>
+        <v>34.99479957449474</v>
       </c>
       <c r="D20" t="n">
-        <v>1.218171965590591</v>
+        <v>1.236272757723244</v>
       </c>
       <c r="E20" t="n">
-        <v>11.65089742133239</v>
+        <v>11.36946394042852</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7592095889247299</v>
+        <v>0.7518059609421162</v>
       </c>
       <c r="G20" t="n">
-        <v>20.51389452349702</v>
+        <v>21.65912487995406</v>
       </c>
       <c r="H20" t="n">
-        <v>37.00833093552596</v>
+        <v>38.00041491267951</v>
       </c>
       <c r="I20" t="n">
-        <v>1.278428446483798</v>
+        <v>1.484754707872102</v>
       </c>
       <c r="J20" t="n">
-        <v>4.745059930779561</v>
+        <v>4.698787255888227</v>
       </c>
       <c r="K20" t="n">
-        <v>22.82600718786596</v>
+        <v>20.79937558451222</v>
       </c>
       <c r="L20" t="n">
-        <v>43.00807092325496</v>
+        <v>44.15636392511983</v>
       </c>
       <c r="M20" t="n">
-        <v>99.95740923640942</v>
+        <v>99.95053908412679</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.86942540373514</v>
+        <v>76.30152344484694</v>
       </c>
       <c r="C21" t="n">
-        <v>37.56977087434019</v>
+        <v>32.32378250005601</v>
       </c>
       <c r="D21" t="n">
-        <v>1.219117858975765</v>
+        <v>1.132285519596179</v>
       </c>
       <c r="E21" t="n">
-        <v>13.53594096328655</v>
+        <v>10.61946590534481</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7597991044844447</v>
+        <v>0.7522125536431378</v>
       </c>
       <c r="G21" t="n">
-        <v>22.08408534587242</v>
+        <v>19.83729991257108</v>
       </c>
       <c r="H21" t="n">
-        <v>38.59132945561154</v>
+        <v>38.02096634768001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.930408272476645</v>
+        <v>1.237964745742125</v>
       </c>
       <c r="J21" t="n">
-        <v>4.748744403027779</v>
+        <v>4.701328460269612</v>
       </c>
       <c r="K21" t="n">
-        <v>17.13057459626485</v>
+        <v>23.69847655515305</v>
       </c>
       <c r="L21" t="n">
-        <v>45.23535751270754</v>
+        <v>43.93649775846116</v>
       </c>
       <c r="M21" t="n">
-        <v>99.93570298331258</v>
+        <v>99.95875681367022</v>
       </c>
     </row>
   </sheetData>
